--- a/teacher_forms/014_e_learning_session_feedback_form--teacher_forms.xlsx
+++ b/teacher_forms/014_e_learning_session_feedback_form--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'ratings-1',_'label':_'1/5'}</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'ratings-1', 'label': '1/5'}</t>
+          <t>1/5</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'ratings-2',_'label':_'2/5'}</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'ratings-2', 'label': '2/5'}</t>
+          <t>2/5</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'ratings-3',_'label':_'3/5'}</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'ratings-3', 'label': '3/5'}</t>
+          <t>3/5</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'ratings-4',_'label':_'4/5'}</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'ratings-4', 'label': '4/5'}</t>
+          <t>4/5</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'ratings-5',_'label':_'5/5'}</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'ratings-5', 'label': '5/5'}</t>
+          <t>5/5</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'ratings-6',_'label':_'1/5'}</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'ratings-6', 'label': '1/5'}</t>
+          <t>1/5</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'ratings-7',_'label':_'2/5'}</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'ratings-7', 'label': '2/5'}</t>
+          <t>2/5</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'ratings-8',_'label':_'3/5'}</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'ratings-8', 'label': '3/5'}</t>
+          <t>3/5</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'ratings-9',_'label':_'4/5'}</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'ratings-9', 'label': '4/5'}</t>
+          <t>4/5</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'ratings-10',_'label':_'5/5'}</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'ratings-10', 'label': '5/5'}</t>
+          <t>5/5</t>
         </is>
       </c>
     </row>
